--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_92_R10.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_92_R10.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.1112</v>
+        <v>7.3861</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9366</v>
+        <v>7.8501</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1746</v>
+        <v>-0.464</v>
       </c>
       <c r="G2" t="n">
         <v>1.8756</v>
@@ -610,13 +610,13 @@
         <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>2.9315</v>
+        <v>2.2064</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2151</v>
+        <v>1.1286</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7164</v>
+        <v>1.0778</v>
       </c>
       <c r="V2" t="n">
         <v>2.1444</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.6713</v>
+        <v>6.0245</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2016</v>
+        <v>6.3195</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5303</v>
+        <v>-0.295</v>
       </c>
       <c r="G3" t="n">
         <v>5.1277</v>
@@ -688,13 +688,13 @@
         <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0075</v>
+        <v>0.3607</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2082</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2157</v>
+        <v>0.4509</v>
       </c>
       <c r="V3" t="n">
         <v>0.5361</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6462</v>
+        <v>3.7641</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2839</v>
+        <v>3.4019</v>
       </c>
       <c r="F4" t="n">
         <v>0.3622</v>
@@ -766,10 +766,10 @@
         <v>0.232</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2399</v>
+        <v>-0.1219</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U4" t="n">
         <v>0.0589</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. PALATIN</t>
+          <t>V. MICIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9784</v>
+        <v>2.4512</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6162</v>
+        <v>3.1163</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3622</v>
+        <v>-0.6651</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6614</v>
+        <v>-0.2068</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9651999999999999</v>
+        <v>-1.6723</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6266</v>
+        <v>1.4654</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0539</v>
+        <v>1.7595</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.7863</v>
+        <v>-0.1275</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8402</v>
+        <v>1.887</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6075</v>
+        <v>-1.9664</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1788</v>
+        <v>-1.5448</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7863</v>
+        <v>-0.4216</v>
       </c>
       <c r="P5" t="n">
         <v>0.232</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6212</v>
+        <v>0.8178</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5623</v>
+        <v>0.9082</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0589</v>
+        <v>-0.0905</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5361</v>
+        <v>1.6083</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. OTURU</t>
+          <t>I. WAINRIGHT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4784</v>
+        <v>1.6499</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3635</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8851</v>
+        <v>1.0365</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3522</v>
+        <v>-0.796</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6264999999999999</v>
+        <v>-0.7692</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2743</v>
+        <v>-0.0268</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3185</v>
+        <v>0.6918</v>
       </c>
       <c r="K6" t="n">
-        <v>2.1713</v>
+        <v>1.3444</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1472</v>
+        <v>-0.6526</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9664</v>
+        <v>-1.4878</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5448</v>
+        <v>-2.1136</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4216</v>
+        <v>0.6258</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5901</v>
+        <v>0.4795</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2923</v>
+        <v>-0.0784</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2978</v>
+        <v>0.5579</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5361</v>
+        <v>0.1107</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.6083</v>
+        <v>0.1107</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. MICIC</t>
+          <t>G. PALATIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3417</v>
+        <v>1.5066</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1413</v>
+        <v>1.1444</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7996</v>
+        <v>0.3622</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2068</v>
+        <v>1.6614</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.6723</v>
+        <v>-0.9651999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4654</v>
+        <v>2.6266</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7595</v>
+        <v>1.0539</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1275</v>
+        <v>-0.7863</v>
       </c>
       <c r="L7" t="n">
-        <v>1.887</v>
+        <v>1.8402</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9664</v>
+        <v>0.6075</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5448</v>
+        <v>-0.1788</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4216</v>
+        <v>0.7863</v>
       </c>
       <c r="P7" t="n">
         <v>0.232</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2917</v>
+        <v>0.1494</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0668</v>
+        <v>0.0905</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2249</v>
+        <v>0.0589</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6083</v>
+        <v>-0.5361</v>
       </c>
       <c r="W7" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MOTLEY</t>
+          <t>B. TIMOR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2894</v>
+        <v>1.4704</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0886</v>
+        <v>1.8467</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7992</v>
+        <v>-0.3763</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2509</v>
+        <v>2.4325</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7696</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5187</v>
+        <v>2.4325</v>
       </c>
       <c r="J8" t="n">
-        <v>0.737</v>
+        <v>1.8034</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1113</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6257</v>
+        <v>1.8034</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9879</v>
+        <v>0.6291</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8809</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.107</v>
+        <v>0.6291</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.7001</v>
+        <v>0.11</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4391</v>
+        <v>0.0433</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2609</v>
+        <v>0.0668</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0722</v>
+        <v>-1.0722</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. TIMOR</t>
+          <t>J. MOTLEY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.218</v>
+        <v>1.0342</v>
       </c>
       <c r="E9" t="n">
-        <v>1.7288</v>
+        <v>1.7661</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5108</v>
+        <v>-0.732</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4325</v>
+        <v>-1.2509</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-1.7696</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4325</v>
+        <v>0.5187</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8034</v>
+        <v>0.737</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.1113</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8034</v>
+        <v>0.6257</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6291</v>
+        <v>-1.9879</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-1.8809</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6291</v>
+        <v>-0.107</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1423</v>
+        <v>1.4449</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0747</v>
+        <v>1.1167</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0677</v>
+        <v>0.3282</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0722</v>
+        <v>1.0722</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. WAINRIGHT</t>
+          <t>T. ODIASE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1616</v>
+        <v>0.6249</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2596</v>
+        <v>-0.4906</v>
       </c>
       <c r="F10" t="n">
-        <v>0.902</v>
+        <v>1.1155</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.796</v>
+        <v>-1.3605</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7692</v>
+        <v>-1.9662</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0268</v>
+        <v>0.6057</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6918</v>
+        <v>-0.2734</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3444</v>
+        <v>-0.5679</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6526</v>
+        <v>0.2944</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4878</v>
+        <v>-1.087</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.1136</v>
+        <v>-1.3983</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6258</v>
+        <v>0.3113</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.2869</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4323</v>
+        <v>-0.1296</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4235</v>
+        <v>0.4165</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1107</v>
+        <v>1.4665</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1107</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. ODIASE</t>
+          <t>D. OTURU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6578000000000001</v>
+        <v>0.4825</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7265</v>
+        <v>2.5693</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3843</v>
+        <v>-2.0867</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3605</v>
+        <v>0.3522</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.9662</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6057</v>
+        <v>-0.2743</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2734</v>
+        <v>2.3185</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5679</v>
+        <v>2.1713</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2944</v>
+        <v>0.1472</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.087</v>
+        <v>-1.9664</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3983</v>
+        <v>-1.5448</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3113</v>
+        <v>-0.4216</v>
       </c>
       <c r="P11" t="n">
-        <v>0.232</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R11" t="n">
         <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3198</v>
+        <v>1.5942</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3655</v>
+        <v>1.498</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6853</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4665</v>
+        <v>-0.5361</v>
       </c>
       <c r="W11" t="n">
         <v>1.0722</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3943</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.7269</v>
+        <v>-0.308</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1005</v>
+        <v>2.4857</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.8274</v>
+        <v>-2.7938</v>
       </c>
       <c r="G12" t="n">
         <v>-1.7805</v>
@@ -1390,13 +1390,13 @@
         <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7341</v>
+        <v>1.1529</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6528</v>
+        <v>1.0381</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0813</v>
+        <v>0.1149</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.2381</v>
+        <v>-0.7504</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3416</v>
+        <v>0.4595</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5796</v>
+        <v>-1.2099</v>
       </c>
       <c r="G13" t="n">
         <v>-1.0982</v>
@@ -1468,13 +1468,13 @@
         <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5162</v>
+        <v>-0.0286</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1336</v>
+        <v>-0.0156</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3826</v>
+        <v>-0.013</v>
       </c>
       <c r="V13" t="n">
         <v>1.0722</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>24.589</v>
+        <v>25.336</v>
       </c>
       <c r="E14" t="n">
-        <v>30.3357</v>
+        <v>31.0823</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.7467</v>
+        <v>-5.7464</v>
       </c>
       <c r="G14" t="n">
         <v>9.628499999999999</v>
@@ -1534,7 +1534,7 @@
         <v>-17.344</v>
       </c>
       <c r="O14" t="n">
-        <v>1.0212</v>
+        <v>1.021200000000001</v>
       </c>
       <c r="P14" t="n">
         <v>2.3196</v>
@@ -1546,16 +1546,16 @@
         <v>13.9172</v>
       </c>
       <c r="S14" t="n">
-        <v>7.705400000000001</v>
+        <v>8.452199999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>4.5818</v>
+        <v>5.3287</v>
       </c>
       <c r="U14" t="n">
         <v>3.1235</v>
       </c>
       <c r="V14" t="n">
-        <v>4.935600000000001</v>
+        <v>4.9356</v>
       </c>
       <c r="W14" t="n">
         <v>11.3999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3626</v>
+        <v>2.487</v>
       </c>
       <c r="E15" t="n">
-        <v>2.754</v>
+        <v>2.9899</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3913</v>
+        <v>-0.5029</v>
       </c>
       <c r="G15" t="n">
         <v>-0.3442</v>
@@ -1624,13 +1624,13 @@
         <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.203</v>
+        <v>-0.0786</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.507</v>
+        <v>-0.2711</v>
       </c>
       <c r="U15" t="n">
-        <v>0.304</v>
+        <v>0.1924</v>
       </c>
       <c r="V15" t="n">
         <v>1.7501</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1772</v>
+        <v>1.2051</v>
       </c>
       <c r="E16" t="n">
-        <v>4.9693</v>
+        <v>4.6155</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.7921</v>
+        <v>-3.4104</v>
       </c>
       <c r="G16" t="n">
         <v>2.1091</v>
@@ -1702,13 +1702,13 @@
         <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4112</v>
+        <v>-0.3833</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4367</v>
+        <v>0.0828</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8478</v>
+        <v>-0.4661</v>
       </c>
       <c r="V16" t="n">
         <v>-2.1444</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. SEDEKERSKIS</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.893</v>
+        <v>-0.83</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2934</v>
+        <v>2.3189</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5996</v>
+        <v>-3.1489</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0897</v>
+        <v>0.5357</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6364</v>
+        <v>0.7131</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7261</v>
+        <v>-0.1774</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3654</v>
+        <v>3.6207</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5629</v>
+        <v>2.3226</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1975</v>
+        <v>1.2981</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4551</v>
+        <v>-3.0849</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9265</v>
+        <v>-1.6095</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5286</v>
+        <v>-1.4755</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4639</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R18" t="n">
         <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.195</v>
+        <v>-1.1185</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4991</v>
+        <v>-0.503</v>
       </c>
       <c r="U18" t="n">
-        <v>0.304</v>
+        <v>-0.6155</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0722</v>
+        <v>1.6083</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.6805</v>
       </c>
       <c r="X18" t="n">
         <v>-1.0722</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. KURUCS</t>
+          <t>T. SEDEKERSKIS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5425</v>
+        <v>-0.8867</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2467</v>
+        <v>-0.1755</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.7892</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5175999999999999</v>
+        <v>-0.0897</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7036</v>
+        <v>0.6364</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2212</v>
+        <v>-0.7261</v>
       </c>
       <c r="J19" t="n">
-        <v>3.2175</v>
+        <v>1.3654</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9662</v>
+        <v>1.5629</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2514</v>
+        <v>-0.1975</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.7352</v>
+        <v>-1.4551</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2626</v>
+        <v>-0.9265</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.4726</v>
+        <v>-0.5286</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4639</v>
+        <v>0.4639</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.1887</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1889</v>
+        <v>-0.3811</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7499</v>
+        <v>0.1924</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>R. KURUCS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5821</v>
+        <v>-1.6154</v>
       </c>
       <c r="E20" t="n">
-        <v>2.083</v>
+        <v>1.8928</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.6651</v>
+        <v>-3.5083</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5357</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7131</v>
+        <v>0.7036</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1774</v>
+        <v>-1.2212</v>
       </c>
       <c r="J20" t="n">
-        <v>3.6207</v>
+        <v>3.2175</v>
       </c>
       <c r="K20" t="n">
-        <v>2.3226</v>
+        <v>1.9662</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2981</v>
+        <v>1.2514</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.0849</v>
+        <v>-3.7352</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.6095</v>
+        <v>-1.2626</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4755</v>
+        <v>-2.4726</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.8556</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.8705</v>
+        <v>-0.6339</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7389</v>
+        <v>-0.165</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1316</v>
+        <v>-0.4689</v>
       </c>
       <c r="V20" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.6805</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9647</v>
+        <v>-1.9419</v>
       </c>
       <c r="E21" t="n">
         <v>-0.1076</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8571</v>
+        <v>-1.8343</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0837</v>
@@ -2092,13 +2092,13 @@
         <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4867</v>
+        <v>-0.4639</v>
       </c>
       <c r="T21" t="n">
         <v>-0.507</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0202</v>
+        <v>0.0431</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3943</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4101</v>
+        <v>-2.2528</v>
       </c>
       <c r="E22" t="n">
         <v>0.0704</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4805</v>
+        <v>-2.3232</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6445</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1573</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1573</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>-1.6083</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3623</v>
+        <v>-2.829</v>
       </c>
       <c r="E23" t="n">
-        <v>1.119</v>
+        <v>1.237</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.4813</v>
+        <v>-4.0659</v>
       </c>
       <c r="G23" t="n">
         <v>0.8951</v>
@@ -2248,13 +2248,13 @@
         <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6311</v>
+        <v>-1.0978</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5975</v>
+        <v>-0.4795</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0337</v>
+        <v>-0.6183</v>
       </c>
       <c r="V23" t="n">
         <v>-1.4665</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>K. DIOP</t>
+          <t>M. HOWARD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.3129</v>
+        <v>-5.2234</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3237</v>
+        <v>-2.784</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.9892</v>
+        <v>-2.4394</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.3466</v>
+        <v>-4.1317</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.4896</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.857</v>
+        <v>-4.0321</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.0437</v>
+        <v>-1.4044</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.0805</v>
+        <v>0.995</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0368</v>
+        <v>-2.3994</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.3028</v>
+        <v>-2.7273</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.4091</v>
+        <v>-1.0945</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.8938</v>
+        <v>-1.6327</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3427</v>
+        <v>-0.2515</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0395</v>
+        <v>-0.2199</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3822</v>
+        <v>-0.0316</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. HOWARD</t>
+          <t>K. DIOP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.869</v>
+        <v>-5.493</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.1379</v>
+        <v>-2.7955</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.7311</v>
+        <v>-2.6975</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.1317</v>
+        <v>-3.3466</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.09959999999999999</v>
+        <v>-1.4896</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.0321</v>
+        <v>-1.857</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.4044</v>
+        <v>-0.0437</v>
       </c>
       <c r="K25" t="n">
-        <v>0.995</v>
+        <v>-0.0805</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.3994</v>
+        <v>0.0368</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.7273</v>
+        <v>-3.3028</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.0945</v>
+        <v>-1.4091</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.6327</v>
+        <v>-1.8938</v>
       </c>
       <c r="P25" t="n">
-        <v>0.232</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8971</v>
+        <v>-0.5228</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5737</v>
+        <v>-0.4323</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3233</v>
+        <v>-0.0905</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.9041</v>
+        <v>-5.5617</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.1535</v>
+        <v>-3.0356</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.7506</v>
+        <v>-2.5261</v>
       </c>
       <c r="G26" t="n">
         <v>-3.8797</v>
@@ -2482,13 +2482,13 @@
         <v>0.232</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5605</v>
+        <v>-0.2181</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2908</v>
+        <v>-0.1729</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2697</v>
+        <v>-0.0452</v>
       </c>
       <c r="V26" t="n">
         <v>-0.5361</v>
@@ -2515,19 +2515,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-24.5891</v>
+        <v>-22.23</v>
       </c>
       <c r="E27" t="n">
-        <v>5.210299999999999</v>
+        <v>5.210299999999998</v>
       </c>
       <c r="F27" t="n">
-        <v>-29.7993</v>
+        <v>-27.4403</v>
       </c>
       <c r="G27" t="n">
         <v>-9.6287</v>
       </c>
       <c r="H27" t="n">
-        <v>6.3985</v>
+        <v>6.398499999999998</v>
       </c>
       <c r="I27" t="n">
         <v>-16.0272</v>
@@ -2551,7 +2551,7 @@
         <v>-15.0059</v>
       </c>
       <c r="P27" t="n">
-        <v>-2.319399999999999</v>
+        <v>-2.3194</v>
       </c>
       <c r="Q27" t="n">
         <v>-13.9173</v>
@@ -2560,19 +2560,19 @@
         <v>11.598</v>
       </c>
       <c r="S27" t="n">
-        <v>-7.7053</v>
+        <v>-5.3463</v>
       </c>
       <c r="T27" t="n">
-        <v>-3.1236</v>
+        <v>-3.1237</v>
       </c>
       <c r="U27" t="n">
-        <v>-4.5818</v>
+        <v>-2.2227</v>
       </c>
       <c r="V27" t="n">
         <v>-4.9356</v>
       </c>
       <c r="W27" t="n">
-        <v>5.928199999999999</v>
+        <v>5.9282</v>
       </c>
       <c r="X27" t="n">
         <v>-10.8638</v>
